--- a/astro-site/public/dl/plan-catering-tematico-eventos/plantilla-proveedores-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/plantilla-proveedores-catering-tematico-eventos.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="96 proveedores" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'96 proveedores'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -466,7 +468,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -494,6 +496,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3893,9 +3896,18 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>